--- a/june 2026/LMT_JUNE_26/Sweera.xlsx
+++ b/june 2026/LMT_JUNE_26/Sweera.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E6B6A93-65C0-4BD3-95ED-72224DA5824C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD534CCA-A772-408C-B755-3BB1232E2ECB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3340,7 +3340,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -3368,7 +3368,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -4575,7 +4575,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -4603,7 +4603,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -5810,7 +5810,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -5838,7 +5838,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -7045,7 +7045,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -7073,7 +7073,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -8280,7 +8280,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -8308,7 +8308,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -9515,7 +9515,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -9543,7 +9543,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -10747,7 +10747,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -10775,7 +10775,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -11978,7 +11978,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -12006,7 +12006,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -13209,7 +13209,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -13237,7 +13237,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -14440,7 +14440,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -14468,7 +14468,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -18421,7 +18421,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -18449,7 +18449,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -19652,7 +19652,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -19680,7 +19680,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -20883,7 +20883,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -20911,7 +20911,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -22114,7 +22114,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -22142,7 +22142,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -23350,7 +23350,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -23378,7 +23378,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -23642,7 +23642,7 @@
       </c>
       <c r="U15" s="163">
         <f>+'2'!P35</f>
-        <v>47407.507305299994</v>
+        <v>38571.672327299995</v>
       </c>
       <c r="XFD15" t="s">
         <v>81</v>
@@ -23823,15 +23823,15 @@
       <c r="G18" s="113"/>
       <c r="H18" s="171">
         <f>+'1'!H18+'2'!H18+'4'!H18+'3'!H18+'5'!H18+'6'!H18+'7'!H18+'8'!H18+'9'!H18+'10'!H18+'11'!H18+'12'!H18+'13'!H18+'14'!H18+'15'!H18+'16'!H18</f>
-        <v>280</v>
+        <v>120</v>
       </c>
       <c r="I18" s="1">
         <f t="shared" si="1"/>
-        <v>14689.5</v>
+        <v>6295.5</v>
       </c>
       <c r="J18" s="171">
         <f>+'1'!J18+'2'!J18+'4'!J18+'3'!J18+'5'!J18+'6'!J18+'7'!J18+'8'!J18+'9'!J18+'10'!J18+'11'!J18+'12'!J18+'13'!J18+'14'!J18+'15'!J18+'16'!J18+'17'!J18+'18'!J18</f>
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="K18" s="171">
         <f>+'1'!K18+'2'!K18+'4'!K18+'3'!K18+'5'!K18+'6'!K18+'7'!K18+'8'!K18+'9'!K18+'10'!K18</f>
@@ -23839,23 +23839,23 @@
       </c>
       <c r="L18" s="174">
         <f>+'1'!L18+'2'!L18+'4'!L18+'3'!L18+'5'!L18+'6'!L18+'7'!L18+'8'!L18+'9'!L18+'10'!L18</f>
-        <v>1762.7399999999998</v>
+        <v>755.46</v>
       </c>
       <c r="M18" s="117">
         <f t="shared" si="2"/>
-        <v>12926.76</v>
+        <v>5540.04</v>
       </c>
       <c r="N18" s="100">
         <f>+'1'!N18+'2'!N18+'4'!N18+'3'!N18+'5'!N18+'6'!N18+'7'!N18+'8'!N18+'9'!N18+'10'!N18</f>
-        <v>2421.2492999999999</v>
+        <v>1016.0937</v>
       </c>
       <c r="O18" s="100">
         <f>+'1'!O18+'2'!O18+'4'!O18+'3'!O18+'5'!O18+'6'!O18+'7'!O18+'8'!O18+'9'!O18+'10'!O18</f>
-        <v>76.740046500000005</v>
+        <v>32.780668500000004</v>
       </c>
       <c r="P18" s="119">
         <f t="shared" si="0"/>
-        <v>15424.749346499999</v>
+        <v>6588.9143684999999</v>
       </c>
       <c r="T18" s="162" t="str">
         <f>+'5'!A5</f>
@@ -24293,7 +24293,7 @@
       <c r="B25" s="210"/>
       <c r="C25" s="211">
         <f>H25/40</f>
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D25" s="205"/>
       <c r="E25" s="205"/>
@@ -24304,15 +24304,15 @@
       </c>
       <c r="H25" s="176">
         <f t="shared" si="3"/>
-        <v>1280</v>
+        <v>1120</v>
       </c>
       <c r="I25" s="177">
         <f t="shared" si="3"/>
-        <v>78199.899999999994</v>
+        <v>69805.899999999994</v>
       </c>
       <c r="J25" s="176">
         <f t="shared" si="3"/>
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="K25" s="177">
         <f t="shared" si="3"/>
@@ -24320,23 +24320,23 @@
       </c>
       <c r="L25" s="178">
         <f t="shared" si="3"/>
-        <v>9164.2999999999993</v>
+        <v>8157.0199999999995</v>
       </c>
       <c r="M25" s="140">
         <f t="shared" si="3"/>
-        <v>68925.755999999994</v>
+        <v>61539.035999999993</v>
       </c>
       <c r="N25" s="141">
         <f>SUM(N16:N24)</f>
-        <v>12811.96818</v>
+        <v>11406.81258</v>
       </c>
       <c r="O25" s="142">
         <f>SUM(O16:O24)</f>
-        <v>408.68862089999999</v>
+        <v>364.72924289999997</v>
       </c>
       <c r="P25" s="143">
         <f>SUM(P16:P24)</f>
-        <v>82146.412800899998</v>
+        <v>73310.577822899999</v>
       </c>
       <c r="T25" s="162" t="str">
         <f>+'12'!A5</f>
@@ -24466,7 +24466,7 @@
       </c>
       <c r="U30" s="164">
         <f>SUM(U14:U28)</f>
-        <v>82146.412800899998</v>
+        <v>73310.577822899999</v>
       </c>
     </row>
     <row r="31" spans="1:21 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -24499,7 +24499,7 @@
       <c r="O32" s="222"/>
       <c r="P32" s="151">
         <f>I25</f>
-        <v>78199.899999999994</v>
+        <v>69805.899999999994</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24520,7 +24520,7 @@
       <c r="O33" s="224"/>
       <c r="P33" s="152">
         <f>L25</f>
-        <v>9164.2999999999993</v>
+        <v>8157.0199999999995</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24563,7 +24563,7 @@
       <c r="O35" s="224"/>
       <c r="P35" s="152">
         <f>P32-P33-P34</f>
-        <v>68925.755999999994</v>
+        <v>61539.036</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24588,7 +24588,7 @@
       </c>
       <c r="P36" s="152">
         <f>N25</f>
-        <v>12811.96818</v>
+        <v>11406.81258</v>
       </c>
     </row>
     <row r="37" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24610,7 +24610,7 @@
       <c r="O37" s="226"/>
       <c r="P37" s="152">
         <f>P35+P36</f>
-        <v>81737.72417999999</v>
+        <v>72945.848580000005</v>
       </c>
     </row>
     <row r="38" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -24635,7 +24635,7 @@
       </c>
       <c r="P38" s="152">
         <f>O38*P37</f>
-        <v>2043.4431044999999</v>
+        <v>1823.6462145000003</v>
       </c>
     </row>
     <row r="39" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -24645,7 +24645,7 @@
       <c r="O39" s="204"/>
       <c r="P39" s="159">
         <f>P37+P38</f>
-        <v>83781.167284499985</v>
+        <v>74769.494794500002</v>
       </c>
     </row>
     <row r="40" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -24817,7 +24817,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -24845,7 +24845,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -26051,8 +26051,7 @@
       <c r="L4" s="229"/>
       <c r="M4" s="229"/>
       <c r="N4" s="243">
-        <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46179</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -26079,8 +26078,8 @@
       <c r="L5" s="229"/>
       <c r="M5" s="229"/>
       <c r="N5" s="243">
-        <f ca="1">N4-1</f>
-        <v>46195</v>
+        <f>N4-1</f>
+        <v>46178</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -26382,6 +26381,7 @@
         <v>4197</v>
       </c>
       <c r="J16" s="102">
+        <f>H16/20</f>
         <v>4</v>
       </c>
       <c r="K16" s="103">
@@ -26445,19 +26445,20 @@
         <f t="shared" ref="I17:I23" si="2">(G17*D17)*F17+H17*F17</f>
         <v>4197</v>
       </c>
-      <c r="J17" s="116">
+      <c r="J17" s="102">
+        <f t="shared" ref="J17:J21" si="3">H17/20</f>
         <v>4</v>
       </c>
       <c r="K17" s="1">
-        <f t="shared" ref="K17:K21" si="3">I17*$K$13</f>
+        <f t="shared" ref="K17:K21" si="4">I17*$K$13</f>
         <v>0</v>
       </c>
       <c r="L17" s="104">
-        <f t="shared" ref="L17:L21" si="4">I17*12%</f>
+        <f t="shared" ref="L17:L21" si="5">I17*12%</f>
         <v>503.64</v>
       </c>
       <c r="M17" s="117">
-        <f t="shared" ref="M17:M23" si="5">I17-K17-L17</f>
+        <f t="shared" ref="M17:M23" si="6">I17-K17-L17</f>
         <v>3693.36</v>
       </c>
       <c r="N17" s="117">
@@ -26465,7 +26466,7 @@
         <v>702.57780000000002</v>
       </c>
       <c r="O17" s="118">
-        <f t="shared" ref="O17:O24" si="6">(N17+M17)*$O$15</f>
+        <f t="shared" ref="O17:O24" si="7">(N17+M17)*$O$15</f>
         <v>21.979689</v>
       </c>
       <c r="P17" s="119">
@@ -26503,38 +26504,39 @@
       </c>
       <c r="G18" s="113"/>
       <c r="H18" s="114">
-        <v>200</v>
+        <v>40</v>
       </c>
       <c r="I18" s="115">
         <f t="shared" si="2"/>
-        <v>10492.5</v>
-      </c>
-      <c r="J18" s="116">
-        <v>10</v>
+        <v>2098.5</v>
+      </c>
+      <c r="J18" s="102">
+        <f t="shared" si="3"/>
+        <v>2</v>
       </c>
       <c r="K18" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L18" s="104">
-        <f t="shared" si="4"/>
-        <v>1259.0999999999999</v>
+        <f t="shared" si="5"/>
+        <v>251.82</v>
       </c>
       <c r="M18" s="117">
-        <f t="shared" si="5"/>
-        <v>9233.4</v>
+        <f t="shared" si="6"/>
+        <v>1846.68</v>
       </c>
       <c r="N18" s="117">
         <f t="shared" si="0"/>
-        <v>1756.4444999999998</v>
+        <v>351.28890000000001</v>
       </c>
       <c r="O18" s="118">
-        <f t="shared" si="6"/>
-        <v>54.949222499999998</v>
+        <f t="shared" si="7"/>
+        <v>10.9898445</v>
       </c>
       <c r="P18" s="119">
         <f t="shared" si="1"/>
-        <v>11044.793722499999</v>
+        <v>2208.9587444999997</v>
       </c>
     </row>
     <row r="19" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -26569,19 +26571,20 @@
         <f t="shared" si="2"/>
         <v>5811.2</v>
       </c>
-      <c r="J19" s="116">
+      <c r="J19" s="102">
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="K19" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L19" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>697.34399999999994</v>
       </c>
       <c r="M19" s="117">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>5113.8559999999998</v>
       </c>
       <c r="N19" s="117">
@@ -26589,7 +26592,7 @@
         <v>972.79487999999992</v>
       </c>
       <c r="O19" s="118">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>30.433254399999996</v>
       </c>
       <c r="P19" s="119">
@@ -26629,19 +26632,20 @@
         <f t="shared" si="2"/>
         <v>5811.2</v>
       </c>
-      <c r="J20" s="116">
+      <c r="J20" s="102">
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="K20" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L20" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>697.34399999999994</v>
       </c>
       <c r="M20" s="117">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>5113.8559999999998</v>
       </c>
       <c r="N20" s="117">
@@ -26649,7 +26653,7 @@
         <v>972.79487999999992</v>
       </c>
       <c r="O20" s="118">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>30.433254399999996</v>
       </c>
       <c r="P20" s="119">
@@ -26689,19 +26693,20 @@
         <f t="shared" si="2"/>
         <v>14528</v>
       </c>
-      <c r="J21" s="116">
+      <c r="J21" s="102">
+        <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="K21" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L21" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1743.36</v>
       </c>
       <c r="M21" s="117">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>12784.64</v>
       </c>
       <c r="N21" s="117">
@@ -26709,7 +26714,7 @@
         <v>2431.9871999999996</v>
       </c>
       <c r="O21" s="118">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>76.083135999999996</v>
       </c>
       <c r="P21" s="119">
@@ -26759,7 +26764,7 @@
         <v>0</v>
       </c>
       <c r="M22" s="117">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="N22" s="117">
@@ -26767,7 +26772,7 @@
         <v>0</v>
       </c>
       <c r="O22" s="118">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="P22" s="119">
@@ -26807,15 +26812,15 @@
       </c>
       <c r="J23" s="116"/>
       <c r="K23" s="1">
-        <f t="shared" ref="K23:K24" si="7">I23*3.5%</f>
+        <f t="shared" ref="K23:K24" si="8">I23*3.5%</f>
         <v>0</v>
       </c>
       <c r="L23" s="119">
-        <f t="shared" ref="L23:L24" si="8">I23*$L$13</f>
+        <f t="shared" ref="L23:L24" si="9">I23*$L$13</f>
         <v>0</v>
       </c>
       <c r="M23" s="117">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="N23" s="117">
@@ -26823,7 +26828,7 @@
         <v>0</v>
       </c>
       <c r="O23" s="118">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="P23" s="119">
@@ -26863,11 +26868,11 @@
       </c>
       <c r="J24" s="129"/>
       <c r="K24" s="130">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L24" s="131">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="M24" s="132">
@@ -26879,7 +26884,7 @@
         <v>0</v>
       </c>
       <c r="O24" s="133">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="P24" s="131">
@@ -26897,41 +26902,41 @@
       <c r="E25" s="205"/>
       <c r="F25" s="246"/>
       <c r="G25" s="134">
-        <f t="shared" ref="G25:M25" si="9">SUM(G16:G24)</f>
+        <f t="shared" ref="G25:M25" si="10">SUM(G16:G24)</f>
         <v>0</v>
       </c>
       <c r="H25" s="135">
-        <f t="shared" si="9"/>
-        <v>720</v>
+        <f t="shared" si="10"/>
+        <v>560</v>
       </c>
       <c r="I25" s="136">
-        <f t="shared" si="9"/>
-        <v>45036.9</v>
+        <f t="shared" si="10"/>
+        <v>36642.9</v>
       </c>
       <c r="J25" s="137"/>
       <c r="K25" s="138">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="L25" s="139">
-        <f t="shared" si="9"/>
-        <v>5404.4279999999999</v>
+        <f t="shared" si="10"/>
+        <v>4397.1480000000001</v>
       </c>
       <c r="M25" s="140">
-        <f t="shared" si="9"/>
-        <v>39632.471999999994</v>
+        <f t="shared" si="10"/>
+        <v>32245.752</v>
       </c>
       <c r="N25" s="141">
         <f>SUM(N16:N24)</f>
-        <v>7539.1770599999982</v>
+        <v>6134.0214599999999</v>
       </c>
       <c r="O25" s="142">
         <f>SUM(O16:O24)</f>
-        <v>235.85824529999999</v>
+        <v>191.89886730000001</v>
       </c>
       <c r="P25" s="143">
         <f>SUM(P16:P24)</f>
-        <v>47407.507305299994</v>
+        <v>38571.672327299995</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -26981,7 +26986,7 @@
       <c r="O28" s="222"/>
       <c r="P28" s="151">
         <f>I25</f>
-        <v>45036.9</v>
+        <v>36642.9</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -27002,7 +27007,7 @@
       <c r="O29" s="224"/>
       <c r="P29" s="152">
         <f>L25</f>
-        <v>5404.4279999999999</v>
+        <v>4397.1480000000001</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -27045,7 +27050,7 @@
       <c r="O31" s="224"/>
       <c r="P31" s="152">
         <f>P28-P29-P30</f>
-        <v>39632.472000000002</v>
+        <v>32245.752</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -27070,7 +27075,7 @@
       </c>
       <c r="P32" s="152">
         <f>N25</f>
-        <v>7539.1770599999982</v>
+        <v>6134.0214599999999</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -27092,7 +27097,7 @@
       <c r="O33" s="226"/>
       <c r="P33" s="152">
         <f>P31+P32</f>
-        <v>47171.649059999996</v>
+        <v>38379.773459999997</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -27117,7 +27122,7 @@
       </c>
       <c r="P34" s="152">
         <f>O34*P33</f>
-        <v>235.85824529999999</v>
+        <v>191.89886729999998</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -27127,7 +27132,7 @@
       <c r="O35" s="204"/>
       <c r="P35" s="159">
         <f>P33+P34</f>
-        <v>47407.507305299994</v>
+        <v>38571.672327299995</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -27299,7 +27304,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -27327,7 +27332,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -28533,7 +28538,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -28561,7 +28566,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -29768,7 +29773,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -29796,7 +29801,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -31003,7 +31008,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -31031,7 +31036,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
